--- a/SuppXLS/Scen_SYS_CarbonBudget-CAP24_450MT-new.xlsx
+++ b/SuppXLS/Scen_SYS_CarbonBudget-CAP24_450MT-new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\TIM-LEAF 060526\tim-leaf 060526\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1213478B-6A40-4BAF-B818-C96BB9C36FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C195B3-A087-4D62-A1CA-3548FC5A8EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="-16310" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
@@ -9409,11 +9409,11 @@
       </c>
       <c r="D4" t="str">
         <f t="shared" ref="D4:E4" si="0" xml:space="preserve"> _xlfn.TEXTJOIN("_",TRUE,"UC","CB",ROUND(D7,0),"Mt",D6)</f>
-        <v>UC_CB_274_Mt_2021-2030</v>
+        <v>UC_CB_476_Mt_2021-2030</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
-        <v>UC_CB_176_Mt_2031-2050</v>
+        <v>UC_CB_-26_Mt_2031-2050</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" ref="F4" si="1" xml:space="preserve"> _xlfn.TEXTJOIN("_",TRUE,"UC","CB",ROUND(F7,0),"Mt",F6)</f>
@@ -9430,11 +9430,11 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" ref="D5:F5" si="2" xml:space="preserve"> _xlfn.TEXTJOIN(" ",TRUE,"Carbon budget",ROUND(D7,0),"Mt",D6)</f>
-        <v>Carbon budget 274 Mt 2021-2030</v>
+        <v>Carbon budget 476 Mt 2021-2030</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="2"/>
-        <v>Carbon budget 176 Mt 2031-2050</v>
+        <v>Carbon budget -26 Mt 2031-2050</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="2"/>
@@ -9468,11 +9468,11 @@
       </c>
       <c r="D7" s="17">
         <f>D24+E24</f>
-        <v>274.2</v>
+        <v>476.2</v>
       </c>
       <c r="E7" s="17">
         <f t="shared" ref="E7" si="3">F24</f>
-        <v>175.8</v>
+        <v>-26.199999999999989</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -9635,16 +9635,16 @@
         <v>69</v>
       </c>
       <c r="D24" s="34">
-        <f>40+54+29+7+30+5.2</f>
-        <v>165.2</v>
+        <f>40+54+29+7+30+5.2+106</f>
+        <v>271.2</v>
       </c>
       <c r="E24" s="34">
-        <f>20+37+23+5+24</f>
-        <v>109</v>
+        <f>20+37+23+5+24+96</f>
+        <v>205</v>
       </c>
       <c r="F24" s="34">
         <f>D19-D24-E24</f>
-        <v>175.8</v>
+        <v>-26.199999999999989</v>
       </c>
       <c r="G24" s="34">
         <v>0</v>
@@ -9823,7 +9823,7 @@
     <row r="9" spans="1:12">
       <c r="B9" t="str">
         <f>"\I:"&amp;VLOOKUP($B$5, config!$B$4:$F$14,3,FALSE) &amp; "_Single"</f>
-        <v>\I:UC_CB_274_Mt_2021-2030_Single</v>
+        <v>\I:UC_CB_476_Mt_2021-2030_Single</v>
       </c>
       <c r="C9" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,3,FALSE)</f>
@@ -9851,11 +9851,11 @@
       </c>
       <c r="K9" s="17">
         <f>VLOOKUP("Value", config!$B$4:$F$14,3,FALSE)*1000</f>
-        <v>274200</v>
+        <v>476200</v>
       </c>
       <c r="L9" t="str">
         <f>VLOOKUP($L$5, config!$B$4:$F$14,3,FALSE) &amp; " - Single"</f>
-        <v>Carbon budget 274 Mt 2021-2030 - Single</v>
+        <v>Carbon budget 476 Mt 2021-2030 - Single</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -9887,7 +9887,7 @@
     <row r="11" spans="1:12">
       <c r="B11" t="str">
         <f>"\I:"&amp;VLOOKUP($B$5, config!$B$4:$F$14,4,FALSE) &amp; "_Single"</f>
-        <v>\I:UC_CB_176_Mt_2031-2050_Single</v>
+        <v>\I:UC_CB_-26_Mt_2031-2050_Single</v>
       </c>
       <c r="C11" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,4,FALSE)</f>
@@ -9915,11 +9915,11 @@
       </c>
       <c r="K11" s="17">
         <f>VLOOKUP("Value", config!$B$4:$F$14,4,FALSE)*1000</f>
-        <v>175800</v>
+        <v>-26199.999999999989</v>
       </c>
       <c r="L11" t="str">
         <f>VLOOKUP($L$5, config!$B$4:$F$14,4,FALSE) &amp; " - Single"</f>
-        <v>Carbon budget 176 Mt 2031-2050 - Single</v>
+        <v>Carbon budget -26 Mt 2031-2050 - Single</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -10176,7 +10176,7 @@
     <row r="9" spans="1:12">
       <c r="B9" t="str">
         <f>VLOOKUP(B$5, config!$B$4:$F$14,3,FALSE) &amp; "_Multi"</f>
-        <v>UC_CB_274_Mt_2021-2030_Multi</v>
+        <v>UC_CB_476_Mt_2021-2030_Multi</v>
       </c>
       <c r="C9" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,3,FALSE)</f>
@@ -10204,11 +10204,11 @@
       </c>
       <c r="K9" s="17">
         <f>VLOOKUP("Value", config!$B$4:$F$14,3,FALSE)*1000</f>
-        <v>274200</v>
+        <v>476200</v>
       </c>
       <c r="L9" t="str">
         <f>VLOOKUP(L$5, config!$B$4:$F$14,3,FALSE) &amp; " - Multi"</f>
-        <v>Carbon budget 274 Mt 2021-2030 - Multi</v>
+        <v>Carbon budget 476 Mt 2021-2030 - Multi</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -10240,7 +10240,7 @@
     <row r="11" spans="1:12">
       <c r="B11" t="str">
         <f>"\I:"&amp;VLOOKUP(B$5, config!$B$4:$F$14,4,FALSE) &amp; "_Multi"</f>
-        <v>\I:UC_CB_176_Mt_2031-2050_Multi</v>
+        <v>\I:UC_CB_-26_Mt_2031-2050_Multi</v>
       </c>
       <c r="C11" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,4,FALSE)</f>
@@ -10268,11 +10268,11 @@
       </c>
       <c r="K11" s="17">
         <f>VLOOKUP("Value", config!$B$4:$F$14,4,FALSE)*1000</f>
-        <v>175800</v>
+        <v>-26199.999999999989</v>
       </c>
       <c r="L11" t="str">
         <f>VLOOKUP(L$5, config!$B$4:$F$14,4,FALSE) &amp; " - Multi"</f>
-        <v>Carbon budget 176 Mt 2031-2050 - Multi</v>
+        <v>Carbon budget -26 Mt 2031-2050 - Multi</v>
       </c>
     </row>
     <row r="12" spans="1:12">
